--- a/data/file_generation/input/data_221/七年级标准1.xlsx
+++ b/data/file_generation/input/data_221/七年级标准1.xlsx
@@ -1570,18 +1570,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9837AE2A-D6CE-446C-A8D0-1BFE9006C4C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15CAB6FE-5CA4-4BC1-BA00-7B394BF22E8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0152206-621A-4113-B881-1D7B0600071C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3557ECEF-4B51-4040-ADB6-0A4D32CDFBAE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CAD7CA-639D-4375-BA8E-3249600C67BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2353822-2082-44BD-83FA-A856AB06E725}"/>
 </file>